--- a/mps-nivel-c/oficial/04_registros/MilhasFacil_Busca-de-Milhas/GEST-MILHASFACIL01-001_Planilha-de-Gestao-do-Projeto.xlsx
+++ b/mps-nivel-c/oficial/04_registros/MilhasFacil_Busca-de-Milhas/GEST-MILHASFACIL01-001_Planilha-de-Gestao-do-Projeto.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identificacao" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipe" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cronograma" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acompanhamento" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medicao" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riscos" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V&amp;V" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GQA" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mudancas" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Identificacao" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Equipe" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cronograma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Acompanhamento" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Backlog" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Medicao" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Riscos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="V&amp;V" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="GQA" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Mudancas" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MILHASFACIL01-001</t>
+          <t>MILHASFACIL01</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>+8,3%</t>
+          <t>+8,5%</t>
         </is>
       </c>
     </row>
